--- a/human_validation/judge/kor/judge_D013_S005_P003__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D013_S005_P003__gemini-3.8-flash_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,166 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 오늘 병원에 오시게 된 이유가 무엇인가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제가 겁이 나서 병원에 오게 된 이유는, 내일 아침 눈을 뜨지 않는 게 차라리 더 간단할지도 모른다는 생각을 하기 시작했기 때문이에요. 저 자신을 해칠 계획이 있는 건 아니지만, 그런 생각들이 마음을 불안하게 만들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 최근에 하루 대부분 우울하거나 슬프거나 가라앉은 기분을 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 네, 거의 매일이요. 차를 끓이거나 정원을 내다보는 것 같은 간단한 일들에도 온통 회색빛 필름이 씌워진 느낌이에요. 그냥 스스로 떨쳐낼 수 없는 조용한 무게감 같은 게 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 이 무거운 느낌을 얼마나 오래 느껴오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 이제 여덟 달 정도 됐어요. 오빠의 건강과 행동이 갑자기 변했을 때쯤 시작됐어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 평소와 확연히 다르게 며칠씩 이어지는 기간 동안 비정상적으로 활력이 넘치거나, 들떠 있거나, 잠을 별로 필요로 하지 않았던 적이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 아니요, 그런 적은 없었던 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 예전에도 이런 식으로 가라앉거나 우울한 느낌을 경험하신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 잘 모르겠어요. 이번과 똑같이 느껴졌던 다른 시기는 딱히 떠오르지 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 예전에 즐기시던 활동들에서 흥미나 즐거움을 잃으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 네. 가끔 수채화 도구를 꺼내긴 하는데, 그냥 종이만 쳐다보다가 다시 치워버려요. 예전에 색감이랑 빛에서 느꼈던 그 즐거움이 이제는 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 요즘 수면 상태는 어떠신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 잠이 고르지 않게 들고, 그러다 자주 새벽 3~4시쯤 깨요. 그때부터 머릿속으로 전화 통화, 서류들, 제가 일을 제대로 처리했는지 같은 생각들을 되짚기 시작해요. 아침이 되면 거의 쉬지 못한 느낌이 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>진단명: 주요우울장애 (D013)
 인구통계: 성별 여성 / 나이 68 / 직업상태 not in workforce / 최종학력 대학원 졸업
@@ -575,215 +726,36 @@
 증상 지속 기간: None
 추가 요건: 
 주호소 증상 코드: S032
-배경 서술: 샬리니의 삽화는 다른 주에 사는 오빠의 건강과 행동에 심각한 변화가 생기면서 시작되었는데, 그녀는 코밸리스에서 의사, 친척들과의 전화 통화 및 재정 관련 서류 정리를 도맡아야 했고, 동시에 가족의 존엄성과 사생활을 지키려 애썼다. 8개월에 걸쳐, 은퇴 생활을 지탱해주던 세심한 일상들 — 아침의 수채화 시간, 정원에서 키운 재료로 요리하기, 시니어 걷기 모임, 후배 교사 멘토링 — 이 점점 줄어들었고, 밤에는 결정들을 되짚어보고 더 일찍 상황 악화를 알아차리지 못한 자신을 탓하며 잠들지 못하는 저녁이 늘어났다. 그녀는 기본적인 의무는 계속 수행했지만, 기분은 계속 가라앉아 있었고 평소 즐기던 활동에서 느끼던 기쁨은 사라졌으며, 죽음과 눈을 뜨고 싶지 않다는 반복적인 생각이 들면서 이것이 단순한 가족 스트레스 이상이라는 것을 인식하게 되었다. 그녀는 시니어 건강검진에서 우울증 선별검사를 받은 후 직접 1차 진료의에게 연락했고, 외래 정신과로 의뢰되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 오늘 병원에 오시게 된 이유가 무엇인가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제가 겁이 나서 병원에 오게 된 이유는, 내일 아침 눈을 뜨지 않는 게 차라리 더 간단할지도 모른다는 생각을 하기 시작했기 때문이에요. 저 자신을 해칠 계획이 있는 건 아니지만, 그런 생각들이 마음을 불안하게 만들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 최근에 하루 대부분 우울하거나 슬프거나 가라앉은 기분을 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 네, 거의 매일이요. 차를 끓이거나 정원을 내다보는 것 같은 간단한 일들에도 온통 회색빛 필름이 씌워진 느낌이에요. 그냥 스스로 떨쳐낼 수 없는 조용한 무게감 같은 게 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 이 무거운 느낌을 얼마나 오래 느껴오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 이제 여덟 달 정도 됐어요. 오빠의 건강과 행동이 갑자기 변했을 때쯤 시작됐어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 평소와 확연히 다르게 며칠씩 이어지는 기간 동안 비정상적으로 활력이 넘치거나, 들떠 있거나, 잠을 별로 필요로 하지 않았던 적이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 아니요, 그런 적은 없었던 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 예전에도 이런 식으로 가라앉거나 우울한 느낌을 경험하신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 잘 모르겠어요. 이번과 똑같이 느껴졌던 다른 시기는 딱히 떠오르지 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 예전에 즐기시던 활동들에서 흥미나 즐거움을 잃으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 네. 가끔 수채화 도구를 꺼내긴 하는데, 그냥 종이만 쳐다보다가 다시 치워버려요. 예전에 색감이랑 빛에서 느꼈던 그 즐거움이 이제는 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 요즘 수면 상태는 어떠신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 잠이 고르지 않게 들고, 그러다 자주 새벽 3~4시쯤 깨요. 그때부터 머릿속으로 전화 통화, 서류들, 제가 일을 제대로 처리했는지 같은 생각들을 되짚기 시작해요. 아침이 되면 거의 쉬지 못한 느낌이 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
+배경 서술: 샬리니의 삽화는 다른 주에 사는 오빠의 건강과 행동에 심각한 변화가 생기면서 시작되었는데, 그녀는 코밸리스에서 의사, 친척들과의 전화 통화 및 재정 관련 서류 정리를 도맡아야 했고, 동시에 가족의 존엄성과 사생활을 지키려 애썼다. 8개월에 걸쳐, 은퇴 생활을 지탱해주던 세심한 일상들 — 아침의 수채화 시간, 정원에서 키운 재료로 요리하기, 시니어 걷기 모임, 후배 교사 멘토링 — 이 점점 줄어들었고, 밤에는 결정들을 되짚어보고 더 일찍 상황 악화를 알아차리지 못한 자신을 탓하며 잠들지 못하는 저녁이 늘어났다. 그녀는 기본적인 의무는 계속 수행했지만, 기분은 계속 가라앉아 있었고 평소 즐기던 활동에서 느끼던 기쁨은 사라졌으며, 죽음과 눈을 뜨고 싶지 않다는 반복적인 생각이 들면서 이것이 단순한 가족 스트레스 이상이라는 것을 인식하게 되었다. 그녀는 시니어 건강검진에서 우울증 선별검사를 받은 후 직접 1차 진료의에게 연락했고, 외래 정신과로 의뢰되었다.
+표집된 증상 목록:
+  - S024 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - S025 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - S027 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - S030 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+  - S032 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
+        </is>
+      </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F32)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=4, 커버리지=0.8)
-  확인된 근거: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.
-  누락: 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.</t>
+          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F32)
+지속 기간 요건: None
+기능적 손상 요건: None
+추가 요건: None
+체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=4, 커버리지=0.8)
+확인된 근거:
+  - 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A37:B37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D013_S005_P003__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D013_S005_P003__gemini-3.8-flash_kor.xlsx
@@ -712,6 +712,11 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -751,11 +756,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A37:B37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D013_S005_P003__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D013_S005_P003__gemini-3.8-flash_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.1649</v>
+        <v>0.1966</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.1944</v>
+        <v>0.2418</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.5417</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
